--- a/GameData/DataTables/Core/UITable.xlsx
+++ b/GameData/DataTables/Core/UITable.xlsx
@@ -2,16 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="144525" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -20,19 +19,14 @@
   <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -60,7 +54,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -135,7 +129,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -177,7 +171,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -209,10 +203,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -244,7 +237,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -425,20 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <cols>
-    <col width="13.125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="15.125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="40.125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="25.5" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="10.5" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="19.25" bestFit="1" customWidth="1" min="8" max="8"/>
-  </cols>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
         </is>
@@ -450,7 +433,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>#</t>
         </is>
@@ -460,7 +443,6 @@
           <t>Id</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>SortOrder</t>
@@ -488,7 +470,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>#</t>
         </is>
@@ -498,7 +480,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>int</t>
@@ -514,7 +495,7 @@
           <t>bool</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -526,71 +507,95 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>Display order relative to group</t>
+          <t>Project UI entries are intentionally empty in the framework baseline.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>同分组内的显示排序</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UI prefab name</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>Hide covered UI in the same group</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>UI group id</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="inlineStr">
-        <is>
-          <t>Allow close by back input</t>
+          <t>界面预制体名称</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>是否暂停被覆盖的界面</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>所属界面分组 Id</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>是否允许返回键关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MainPageShell</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DialogView</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/GameData/DataTables/Core/UITable.xlsx
+++ b/GameData/DataTables/Core/UITable.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,6 +590,32 @@
         <v>2</v>
       </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>20</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BoardPage</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/GameData/DataTables/Core/UITable.xlsx
+++ b/GameData/DataTables/Core/UITable.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -621,6 +621,32 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PreparationPage</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GameData/DataTables/Core/UITable.xlsx
+++ b/GameData/DataTables/Core/UITable.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,6 +647,32 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SettlementPage</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GameData/DataTables/Core/UITable.xlsx
+++ b/GameData/DataTables/Core/UITable.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -673,6 +673,32 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GameData/DataTables/Core/UITable.xlsx
+++ b/GameData/DataTables/Core/UITable.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,6 +699,32 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SaveSlotPage</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GameData/DataTables/Core/UITable.xlsx
+++ b/GameData/DataTables/Core/UITable.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -725,6 +725,344 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>40</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>MapPage</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>HomePage</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="n">
+        <v>40</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>JournalPage</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>11</v>
+      </c>
+      <c r="D15" t="n">
+        <v>40</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>WorkbenchPage</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>12</v>
+      </c>
+      <c r="D16" t="n">
+        <v>40</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CodexPage</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>13</v>
+      </c>
+      <c r="D17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ArchivePage</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D18" t="n">
+        <v>40</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>GuestPage</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>15</v>
+      </c>
+      <c r="D19" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ServicePage</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>16</v>
+      </c>
+      <c r="D20" t="n">
+        <v>30</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>DialoguePage</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>17</v>
+      </c>
+      <c r="D21" t="n">
+        <v>25</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ProloguePage</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>18</v>
+      </c>
+      <c r="D22" t="n">
+        <v>25</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>InvestigationPage</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>19</v>
+      </c>
+      <c r="D23" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RecoveryPage</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>20</v>
+      </c>
+      <c r="D24" t="n">
+        <v>25</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>FeedbackPage</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
